--- a/04_Figures/F06_prediction/modules/acute/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/acute/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -569,13 +563,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.145594224928791</v>
+        <v>-0.150786745077972</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
@@ -602,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.145594224928791</v>
+        <v>-0.150786745077972</v>
       </c>
       <c r="I3" t="n">
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0646766169154229</v>
+        <v>0.63681592039801</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.195166221997047</v>
+        <v>-0.184734486636629</v>
       </c>
       <c r="M3" t="n">
-        <v>0.142329591869978</v>
+        <v>0.158856967377812</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -676,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -688,16 +682,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.278606965174129</v>
+        <v>0.308457711442786</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.174814052188448</v>
+        <v>-0.166273100890346</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0990827182493149</v>
+        <v>0.0719310701244613</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -750,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -762,16 +756,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.621890547263682</v>
+        <v>0.656716417910448</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.170017379021961</v>
+        <v>-0.164091592448928</v>
       </c>
       <c r="M7" t="n">
-        <v>0.100161824900483</v>
+        <v>0.074150223303682</v>
       </c>
     </row>
     <row r="8">
@@ -791,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.222012424761341</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.192857142857143</v>
+        <v>-1</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.222012424761341</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.192857142857143</v>
+        <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.830845771144279</v>
+        <v>0.681592039800995</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0646766169154229</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.170292455086751</v>
+        <v>-0.17825170296822</v>
       </c>
       <c r="M9" t="n">
-        <v>0.147426310191927</v>
+        <v>0.226703715868191</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -898,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -913,13 +907,13 @@
         <v>0.248756218905473</v>
       </c>
       <c r="K11" t="n">
-        <v>0.562189054726368</v>
+        <v>0.472636815920398</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.197260042618837</v>
+        <v>-0.173043432782334</v>
       </c>
       <c r="M11" t="n">
-        <v>0.125583641075958</v>
+        <v>0.105249669704966</v>
       </c>
     </row>
     <row r="12">
@@ -939,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -972,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -984,16 +978,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.587064676616915</v>
+        <v>0.467661691542289</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.159773229495004</v>
+        <v>-0.180351542828549</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00299044193031527</v>
+        <v>0.100960869071023</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.275948749247316</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="4">
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.145025963341674</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.320969275595492</v>
+        <v>-0.333063429847212</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.146270403266856</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="7">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.149350185151416</v>
+        <v>-0.153674704337722</v>
       </c>
     </row>
     <row r="14">
@@ -1158,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.5155239848041</v>
+        <v>-0.308013825543922</v>
       </c>
     </row>
     <row r="15">
@@ -1169,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.173601588540273</v>
       </c>
     </row>
     <row r="16">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.197656611483484</v>
+        <v>-0.156626725005922</v>
       </c>
     </row>
     <row r="17">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.40244632456054</v>
+        <v>-0.0582816302918392</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.380190964041554</v>
+        <v>-0.354301409936957</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.398445612543223</v>
+        <v>-0.204824760130099</v>
       </c>
     </row>
     <row r="21">
@@ -1235,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.26466286788606</v>
+        <v>-0.256363309412587</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.346775330799521</v>
+        <v>-0.302374697093916</v>
       </c>
     </row>
     <row r="23">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.257273366312833</v>
+        <v>-0.508456236323773</v>
       </c>
     </row>
     <row r="24">
@@ -1268,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.217234423851537</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="25">
@@ -1323,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.478697841241702</v>
+        <v>-0.148965647596085</v>
       </c>
     </row>
     <row r="30">
@@ -1345,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.268800887277069</v>
+        <v>-0.162438300194823</v>
       </c>
     </row>
     <row r="32">
@@ -1367,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.272957317014617</v>
+        <v>-0.277451308455843</v>
       </c>
     </row>
     <row r="34">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.247980802138122</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="35">
@@ -1389,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.200983577268502</v>
+        <v>-0.276837879018313</v>
       </c>
     </row>
     <row r="36">
@@ -1400,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.395582917787254</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="37">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.142502020058896</v>
+        <v>-0.145602127073617</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.330754577884971</v>
+        <v>-0.217749524027483</v>
       </c>
     </row>
     <row r="39">
@@ -1444,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.196050327414094</v>
+        <v>-0.213311846865272</v>
       </c>
     </row>
     <row r="41">
@@ -1455,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.229803802387968</v>
       </c>
     </row>
     <row r="42">
@@ -1488,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.141329070126844</v>
       </c>
     </row>
     <row r="45">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.212723852762949</v>
+        <v>-0.264952579945116</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.196894511544009</v>
+        <v>-0.193440110361118</v>
       </c>
     </row>
     <row r="50">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.47136517531251</v>
+        <v>-0.088080229310862</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0602265753370217</v>
+        <v>-0.114570331723172</v>
       </c>
     </row>
     <row r="55">
@@ -1620,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.487049036096899</v>
+        <v>-0.51247792825562</v>
       </c>
     </row>
     <row r="57">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.613385395508104</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="59">
@@ -1664,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.403791983884632</v>
+        <v>-0.256786139044066</v>
       </c>
     </row>
     <row r="61">
@@ -1752,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.171122434923991</v>
+        <v>-0.151187623491291</v>
       </c>
     </row>
     <row r="69">
@@ -1763,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.330178494798411</v>
+        <v>0.170189022274858</v>
       </c>
     </row>
     <row r="70">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.106042897109496</v>
+        <v>-0.198741679328426</v>
       </c>
     </row>
     <row r="72">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.307767032300186</v>
+        <v>-0.335890655757485</v>
       </c>
     </row>
     <row r="75">
@@ -1829,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.467487291523069</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="76">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.293704014972059</v>
+        <v>-0.216351928943152</v>
       </c>
     </row>
     <row r="77">
@@ -1862,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.156970375307578</v>
       </c>
     </row>
     <row r="79">
@@ -1884,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.350482670141708</v>
+        <v>-0.319958462430779</v>
       </c>
     </row>
     <row r="81">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.0259674456331782</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.213038387110871</v>
+        <v>-0.203619974150165</v>
       </c>
     </row>
     <row r="83">
@@ -1928,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.215912388370488</v>
       </c>
     </row>
     <row r="85">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.610834515208319</v>
       </c>
     </row>
     <row r="86">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.181201128405606</v>
+        <v>-0.178344105031516</v>
       </c>
     </row>
     <row r="88">
@@ -1983,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.93582727313166</v>
       </c>
     </row>
     <row r="90">
@@ -2038,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.157486210946526</v>
+        <v>-0.183531420342401</v>
       </c>
     </row>
     <row r="95">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>0.397097687594051</v>
+        <v>0.393167907117896</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.171209297194419</v>
       </c>
     </row>
     <row r="97">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.407033360953089</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="99">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.415251168988348</v>
+        <v>-0.165158510960685</v>
       </c>
     </row>
     <row r="100">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.072651589832291</v>
+        <v>-0.182157982716077</v>
       </c>
     </row>
     <row r="104">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.252652391334293</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="105">
@@ -2159,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.351957321841309</v>
+        <v>-0.510520736696086</v>
       </c>
     </row>
     <row r="106">
@@ -2170,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.187215490745712</v>
+        <v>-0.18817265441745</v>
       </c>
     </row>
     <row r="107">
@@ -2192,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.2064958832933</v>
+        <v>-0.255058834525011</v>
       </c>
     </row>
     <row r="109">
@@ -2203,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.113014485992897</v>
+        <v>-0.244747861526279</v>
       </c>
     </row>
     <row r="110">
@@ -2236,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.154307186758888</v>
+        <v>-0.168503460737463</v>
       </c>
     </row>
     <row r="113">
@@ -2247,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.297393869397989</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="114">
@@ -2269,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.256036582216207</v>
+        <v>-0.227947560915485</v>
       </c>
     </row>
     <row r="116">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.211606747372632</v>
+        <v>-0.206516516256538</v>
       </c>
     </row>
     <row r="119">
@@ -2346,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.178696018189932</v>
+        <v>-0.171114683086389</v>
       </c>
     </row>
     <row r="123">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.163678864665319</v>
+        <v>-0.156945319385052</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.262324590381436</v>
+        <v>-0.214511992253545</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.227743587323013</v>
+        <v>-0.192074647010254</v>
       </c>
     </row>
     <row r="129">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.271110931705338</v>
+        <v>-0.22660484315954</v>
       </c>
     </row>
     <row r="133">
@@ -2489,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.362714336715962</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="136">
@@ -2500,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2216984702419</v>
+        <v>-0.195272482424834</v>
       </c>
     </row>
     <row r="137">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.184421393794739</v>
+        <v>-0.20612788631576</v>
       </c>
     </row>
     <row r="138">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.154491876553262</v>
+        <v>-0.145727084298466</v>
       </c>
     </row>
     <row r="139">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.211426904187371</v>
+        <v>-0.156242426576593</v>
       </c>
     </row>
     <row r="141">
@@ -2588,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.154925332565691</v>
       </c>
     </row>
     <row r="145">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.146229041341898</v>
+        <v>-0.158162005176009</v>
       </c>
     </row>
     <row r="146">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.332983376716815</v>
+        <v>-0.197099482345819</v>
       </c>
     </row>
     <row r="147">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.222821423450864</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="148">
@@ -2643,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.32451812874472</v>
+        <v>-0.857983712120375</v>
       </c>
     </row>
     <row r="150">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.243807748883857</v>
+        <v>-0.269630085819315</v>
       </c>
     </row>
     <row r="151">
@@ -2676,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.722607513935453</v>
+        <v>-0.173747899676956</v>
       </c>
     </row>
     <row r="153">
@@ -2687,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.189897484606382</v>
+        <v>-0.138572559848923</v>
       </c>
     </row>
     <row r="154">
@@ -2720,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.323039277540242</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="157">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.188330569573287</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="158">
@@ -2742,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177718876350181</v>
       </c>
     </row>
     <row r="159">
@@ -2764,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.20011494809534</v>
+        <v>-0.157121100892503</v>
       </c>
     </row>
     <row r="161">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.213402693466513</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.0283431947358181</v>
+        <v>-0.140093810774658</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.154934683820774</v>
+        <v>-0.161725974450896</v>
       </c>
     </row>
     <row r="165">
@@ -2852,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.143976893144854</v>
       </c>
     </row>
     <row r="169">
@@ -2863,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.126623652293893</v>
+        <v>-0.0410533662823802</v>
       </c>
     </row>
     <row r="170">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.158332306349052</v>
+        <v>-0.152592545301149</v>
       </c>
     </row>
     <row r="171">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.240829108393706</v>
+        <v>-0.251443885358839</v>
       </c>
     </row>
     <row r="176">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.188824526133469</v>
+        <v>-0.247016662681823</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.117317868820356</v>
+        <v>-0.204514604340145</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.264530317655774</v>
+        <v>-0.151855799179798</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0794761766702741</v>
+        <v>-0.0190224447335556</v>
       </c>
     </row>
     <row r="184">
@@ -3028,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.324296092928098</v>
       </c>
     </row>
     <row r="185">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.261910434898058</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.186461247343258</v>
+        <v>-0.158166175917503</v>
       </c>
     </row>
     <row r="188">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.272040437960311</v>
+        <v>-0.191835255057449</v>
       </c>
     </row>
     <row r="190">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.26603569635414</v>
+        <v>-0.373182054111978</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.422142953234182</v>
+        <v>-0.362719247006565</v>
       </c>
     </row>
     <row r="193">
@@ -3149,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.237355027405558</v>
+        <v>-0.181302964702234</v>
       </c>
     </row>
     <row r="196">
@@ -3160,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.167374366421804</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="197">
@@ -3193,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.223095465459011</v>
       </c>
     </row>
     <row r="200">
@@ -3204,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.37363287987428</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="201">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.391571162313283</v>
+        <v>-0.173870668023924</v>
       </c>
     </row>
     <row r="202">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.378939305915131</v>
+        <v>-0.366701026600537</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.184741475374863</v>
+        <v>-0.18762456628268</v>
       </c>
     </row>
     <row r="205">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.581995968947312</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="207">
@@ -3281,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.228692889762354</v>
       </c>
     </row>
     <row r="208">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.149012203991317</v>
+        <v>-0.150360832489605</v>
       </c>
     </row>
     <row r="209">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.166166181209243</v>
+        <v>-0.131350752234396</v>
       </c>
     </row>
     <row r="210">
@@ -3325,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.449586949148863</v>
+        <v>-0.382629410383118</v>
       </c>
     </row>
     <row r="212">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.165523600382129</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="214">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.177515501832021</v>
+        <v>-0.113131342719939</v>
       </c>
     </row>
     <row r="215">
@@ -3369,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.169224828059198</v>
+        <v>-0.168127155512123</v>
       </c>
     </row>
     <row r="216">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.18297773112096</v>
+        <v>-0.132641946537468</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.219084917502833</v>
+        <v>-0.177064357754909</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.324979461600872</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="221">
@@ -3523,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.244854092807413</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="230">
@@ -3545,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.276810633839524</v>
+        <v>-0.319821977368491</v>
       </c>
     </row>
     <row r="232">
@@ -3567,7 +3561,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.219367067493936</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="234">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.278981848984095</v>
+        <v>-0.241404674990215</v>
       </c>
     </row>
     <row r="235">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.184354920142891</v>
+        <v>-0.285170160191197</v>
       </c>
     </row>
     <row r="236">
@@ -3600,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.27028985569161</v>
+        <v>-0.24534977782632</v>
       </c>
     </row>
     <row r="237">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.292508894547278</v>
+        <v>-0.640903842936964</v>
       </c>
     </row>
     <row r="238">
@@ -3622,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.180421395272754</v>
+        <v>-0.149711179684592</v>
       </c>
     </row>
     <row r="239">
@@ -3644,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.251267146770769</v>
+        <v>-0.18035863007767</v>
       </c>
     </row>
     <row r="241">
@@ -3655,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.488827242548361</v>
+        <v>-0.21777438444292</v>
       </c>
     </row>
     <row r="242">
@@ -3688,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.156335155078705</v>
+        <v>-0.0735666626367506</v>
       </c>
     </row>
     <row r="245">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.0292854702149237</v>
+        <v>0.0114014855407927</v>
       </c>
     </row>
     <row r="250">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.286263575429973</v>
+        <v>-0.105177761918099</v>
       </c>
     </row>
     <row r="254">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.192367633273856</v>
+        <v>-0.172173597149207</v>
       </c>
     </row>
     <row r="255">
@@ -3853,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.183893252854194</v>
+        <v>-0.154143902938542</v>
       </c>
     </row>
     <row r="260">
@@ -3864,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.269112079990971</v>
+        <v>-0.153112086743645</v>
       </c>
     </row>
     <row r="261">
@@ -3875,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.161128516975317</v>
+        <v>-0.280871022485504</v>
       </c>
     </row>
     <row r="262">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.322333548636037</v>
+        <v>-0.149225743196929</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.558099171037876</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.358422467197082</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.103869977896912</v>
+        <v>-0.0682970193769123</v>
       </c>
     </row>
     <row r="269">
@@ -3963,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.180125083700799</v>
+        <v>-0.177565122127284</v>
       </c>
     </row>
     <row r="270">
@@ -3985,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.196569143595581</v>
+        <v>-0.172181447886865</v>
       </c>
     </row>
     <row r="272">
@@ -3996,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.162490263004331</v>
       </c>
     </row>
     <row r="273">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.371498936355653</v>
+        <v>-0.410358378735414</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.28035179460033</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="276">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.167896343990976</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.409023185326948</v>
       </c>
     </row>
     <row r="286">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.152509438663697</v>
+        <v>-0.164647461599239</v>
       </c>
     </row>
     <row r="288">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.176112549802343</v>
+        <v>-0.184825993103878</v>
       </c>
     </row>
     <row r="296">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.442503531222755</v>
+        <v>-0.184879376495271</v>
       </c>
     </row>
     <row r="300">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.37081747249982</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="301">
@@ -4337,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.32627258984728</v>
+        <v>-0.145079423499837</v>
       </c>
     </row>
     <row r="304">
@@ -4359,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.487722617208674</v>
+        <v>-0.226892778118523</v>
       </c>
     </row>
     <row r="306">
@@ -4370,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.157189783460973</v>
+        <v>-0.221467589634786</v>
       </c>
     </row>
     <row r="307">
@@ -4392,7 +4386,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.246979763885559</v>
       </c>
     </row>
     <row r="309">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150651121673846</v>
       </c>
     </row>
     <row r="310">
@@ -4502,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.16364339835781</v>
+        <v>-0.154920749769458</v>
       </c>
     </row>
     <row r="319">
@@ -4546,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.151234540553054</v>
       </c>
     </row>
     <row r="323">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.148618537192652</v>
+        <v>-0.162750991786022</v>
       </c>
     </row>
     <row r="326">
@@ -4590,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150805675981589</v>
       </c>
     </row>
     <row r="327">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.2636166769531</v>
+        <v>-0.234809338476179</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.280469987034494</v>
+        <v>-0.222388567574996</v>
       </c>
     </row>
     <row r="329">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.282312388851857</v>
+        <v>-0.261737676555277</v>
       </c>
     </row>
     <row r="333">
@@ -4733,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.200769685790801</v>
       </c>
     </row>
     <row r="340">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.278881689863078</v>
+        <v>-0.284935783943314</v>
       </c>
     </row>
     <row r="341">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.426892603389237</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="342">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.301402699486189</v>
+        <v>-0.264639188719514</v>
       </c>
     </row>
     <row r="344">
@@ -4788,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149641907204954</v>
       </c>
     </row>
     <row r="345">
@@ -4799,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.161565128994357</v>
+        <v>-0.13764469779544</v>
       </c>
     </row>
     <row r="346">
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.11301042161622</v>
+        <v>-0.160466221438458</v>
       </c>
     </row>
     <row r="347">
@@ -4843,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.209292700706926</v>
       </c>
     </row>
     <row r="350">
@@ -4865,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.246709048682662</v>
+        <v>-0.227252971736461</v>
       </c>
     </row>
     <row r="352">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.257554032174966</v>
+        <v>-0.198900682478443</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.180490817443188</v>
+        <v>-0.166331148346177</v>
       </c>
     </row>
     <row r="354">
@@ -4898,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.153713525515027</v>
+        <v>-0.15523531568278</v>
       </c>
     </row>
     <row r="355">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.237077050345043</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="357">
@@ -4964,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.0904473892994613</v>
+        <v>-0.0733826860174116</v>
       </c>
     </row>
     <row r="361">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.190416867494857</v>
+        <v>-0.168650579163741</v>
       </c>
     </row>
     <row r="364">
@@ -5008,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.000100188122925227</v>
+        <v>-0.241061402563444</v>
       </c>
     </row>
     <row r="365">
@@ -5052,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.101083794229643</v>
+        <v>-0.244454974461719</v>
       </c>
     </row>
     <row r="369">
@@ -5063,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.212583658117562</v>
+        <v>-0.182285979613509</v>
       </c>
     </row>
     <row r="370">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.178484743113438</v>
       </c>
     </row>
     <row r="371">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.109869192041043</v>
+        <v>-0.108154543624378</v>
       </c>
     </row>
     <row r="376">
@@ -5195,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.163597333051622</v>
+        <v>-0.181504799434838</v>
       </c>
     </row>
     <row r="382">
@@ -5206,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.0327099670992848</v>
+        <v>-0.062560196604843</v>
       </c>
     </row>
     <row r="383">
@@ -5217,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.206016717410206</v>
+        <v>-0.272343825615929</v>
       </c>
     </row>
     <row r="384">
@@ -5261,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.213831098308539</v>
+        <v>-0.135863206038043</v>
       </c>
     </row>
     <row r="388">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>0.482397736813615</v>
+        <v>0.307848993220958</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.215305290354504</v>
+        <v>-0.236942021298095</v>
       </c>
     </row>
     <row r="393">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.151872320185717</v>
+        <v>-0.213552724064018</v>
       </c>
     </row>
     <row r="395">
@@ -5349,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.275589623890226</v>
+        <v>-0.148981045138506</v>
       </c>
     </row>
     <row r="396">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.268241033479068</v>
+        <v>-0.222943126013547</v>
       </c>
     </row>
     <row r="397">
@@ -5382,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.381346111062885</v>
       </c>
     </row>
     <row r="399">
@@ -5393,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.348233463619728</v>
       </c>
     </row>
     <row r="400">
@@ -5404,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.175062714150355</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="401">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.437438894303069</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="404">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.155101247390196</v>
+        <v>-0.185096120990463</v>
       </c>
     </row>
     <row r="405">
@@ -5481,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.185593641419292</v>
       </c>
     </row>
     <row r="408">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.174330764788965</v>
+        <v>-0.154065685905644</v>
       </c>
     </row>
     <row r="409">
@@ -5503,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.148467524389328</v>
       </c>
     </row>
     <row r="410">
@@ -5525,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.439813116349458</v>
+        <v>-0.370722236117754</v>
       </c>
     </row>
     <row r="412">
@@ -5547,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.292201470801963</v>
+        <v>-0.497418098228698</v>
       </c>
     </row>
     <row r="414">
@@ -5558,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.051915159362943</v>
+        <v>-0.219003660856723</v>
       </c>
     </row>
     <row r="415">
@@ -5569,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.253076917634666</v>
+        <v>-0.246798585711856</v>
       </c>
     </row>
     <row r="416">
@@ -5580,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.294470748462106</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="417">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.147592826617672</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="419">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.169149979316862</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="420">
@@ -5657,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.154681075139161</v>
+        <v>-0.174657083433754</v>
       </c>
     </row>
     <row r="424">
@@ -5723,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.164983139717269</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5745,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.172704464065876</v>
+        <v>-0.223153906239611</v>
       </c>
     </row>
     <row r="432">
@@ -5767,7 +5761,7 @@
         <v>16</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.213729585708691</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="434">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.237627435824567</v>
+        <v>-0.287845892579842</v>
       </c>
     </row>
     <row r="436">
@@ -5800,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.233961366408467</v>
+        <v>-0.296879182687102</v>
       </c>
     </row>
     <row r="437">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.23309737958893</v>
+        <v>-0.423154699423148</v>
       </c>
     </row>
     <row r="438">
@@ -5822,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.246911360208534</v>
+        <v>-0.154239608454651</v>
       </c>
     </row>
     <row r="439">
@@ -5844,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.271433043773352</v>
+        <v>-0.216551915233913</v>
       </c>
     </row>
     <row r="441">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.451542241855799</v>
+        <v>-0.241888264696255</v>
       </c>
     </row>
     <row r="442">
@@ -5888,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.146954835153344</v>
+        <v>-0.140710552299927</v>
       </c>
     </row>
     <row r="445">
@@ -5932,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.188954783437576</v>
       </c>
     </row>
     <row r="449">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.159608822368233</v>
+        <v>-0.203322625065228</v>
       </c>
     </row>
     <row r="450">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.140768036135637</v>
+        <v>-0.13993089025797</v>
       </c>
     </row>
     <row r="454">
@@ -5998,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.192506973541229</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="455">
@@ -6009,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.290048877438785</v>
       </c>
     </row>
     <row r="456">
@@ -6042,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.580720555843165</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="459">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.493893937258765</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="467">
@@ -6152,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.0288531137288544</v>
+        <v>-0.119960115392515</v>
       </c>
     </row>
     <row r="469">
@@ -6163,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.317671171399729</v>
+        <v>-0.138681015322837</v>
       </c>
     </row>
     <row r="470">
@@ -6185,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.14894765033592</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="472">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.141429828793728</v>
+        <v>-0.1050941232103</v>
       </c>
     </row>
     <row r="473">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.178639307270685</v>
+        <v>-0.205307638306569</v>
       </c>
     </row>
     <row r="475">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.410525045462249</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6284,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.255666847534701</v>
+        <v>-0.186143629117806</v>
       </c>
     </row>
     <row r="481">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.211835245574092</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6317,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.187164760299114</v>
       </c>
     </row>
     <row r="484">
@@ -6339,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.181110823637043</v>
       </c>
     </row>
     <row r="486">
@@ -6361,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.177458457280371</v>
       </c>
     </row>
     <row r="488">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.182002860263993</v>
+        <v>-0.192927384333828</v>
       </c>
     </row>
     <row r="496">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.500631617440807</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="500">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.368977423607766</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="501">
@@ -6537,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.213662008717836</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="504">
@@ -6548,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.151091264082886</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="505">
@@ -6559,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.304486767259684</v>
+        <v>-0.295450209518081</v>
       </c>
     </row>
     <row r="506">
@@ -6592,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.161822041085399</v>
+        <v>-0.205744661475149</v>
       </c>
     </row>
     <row r="509">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.1531929355346</v>
+        <v>-0.147602300716236</v>
       </c>
     </row>
     <row r="510">
@@ -6702,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.144133996876627</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="519">
@@ -6735,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.234901010284158</v>
       </c>
     </row>
     <row r="522">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.197632866583092</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="525">
@@ -6779,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.195196626595635</v>
+        <v>-0.215893609545676</v>
       </c>
     </row>
     <row r="526">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.219975844002225</v>
+        <v>-0.213751311811992</v>
       </c>
     </row>
     <row r="529">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.382474340802509</v>
+        <v>-0.502362504518699</v>
       </c>
     </row>
     <row r="533">
@@ -6911,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.162222623985605</v>
+        <v>-0.166806968195768</v>
       </c>
     </row>
     <row r="538">
@@ -6944,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.149461908793876</v>
+        <v>-0.18418974717128</v>
       </c>
     </row>
     <row r="541">
@@ -6955,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.34539656412598</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.221932831015603</v>
+        <v>-0.155567877324526</v>
       </c>
     </row>
     <row r="544">
@@ -6999,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.151579991355229</v>
+        <v>-0.180560878313605</v>
       </c>
     </row>
     <row r="546">
@@ -7010,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>0.277860534605249</v>
+        <v>0.218182200763719</v>
       </c>
     </row>
     <row r="547">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.153181652619246</v>
+        <v>-0.538815916405468</v>
       </c>
     </row>
     <row r="550">
@@ -7065,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.341005658939934</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="552">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.224796470545749</v>
+        <v>-0.174300698193858</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.137390042426881</v>
+        <v>-0.167758860891905</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.107299247901024</v>
+        <v>-0.151797936210557</v>
       </c>
     </row>
     <row r="555">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.280734425940074</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.166088299996517</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="558">
@@ -7164,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.19096345497859</v>
+        <v>-0.173188531016263</v>
       </c>
     </row>
     <row r="561">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.181980771614513</v>
+        <v>-0.176986887369401</v>
       </c>
     </row>
     <row r="564">
@@ -7208,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.223034123995874</v>
+        <v>-0.240916619483688</v>
       </c>
     </row>
     <row r="565">
@@ -7241,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.324967551365571</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7252,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.155528285687835</v>
+        <v>-0.190873919364008</v>
       </c>
     </row>
     <row r="569">
@@ -7263,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.178105239778069</v>
+        <v>-0.169291962663459</v>
       </c>
     </row>
     <row r="570">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.181580395794795</v>
       </c>
     </row>
     <row r="571">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.217604213564999</v>
+        <v>-0.160430271944829</v>
       </c>
     </row>
     <row r="576">
@@ -7395,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.175765720285608</v>
       </c>
     </row>
     <row r="582">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>0.348996999215304</v>
+        <v>0.137624000464055</v>
       </c>
     </row>
     <row r="583">
@@ -7417,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.229891260453875</v>
+        <v>-0.210458221972486</v>
       </c>
     </row>
     <row r="584">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.160043660388551</v>
+        <v>-0.154013393007523</v>
       </c>
     </row>
     <row r="588">
@@ -7472,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.204888356323834</v>
+        <v>-0.191595518415604</v>
       </c>
     </row>
     <row r="589">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.181914892842884</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="590">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>0.338626518016517</v>
+        <v>0.197290082214943</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.0614181174826076</v>
       </c>
     </row>
     <row r="593">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.16225636771996</v>
+        <v>-0.225297323243247</v>
       </c>
     </row>
     <row r="595">
@@ -7549,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.254308681254674</v>
+        <v>-0.221859671651508</v>
       </c>
     </row>
     <row r="596">
@@ -7560,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.126614529922533</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="597">
@@ -7582,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.439261048554496</v>
+        <v>-0.386336471106882</v>
       </c>
     </row>
     <row r="599">
@@ -7593,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.311096496489816</v>
       </c>
     </row>
     <row r="600">
@@ -7670,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.139958716860239</v>
+        <v>-0.140353077777569</v>
       </c>
     </row>
     <row r="607">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.582483993513872</v>
+        <v>-0.291399565187175</v>
       </c>
     </row>
     <row r="610">
@@ -7747,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.18750671416585</v>
+        <v>-0.149175687759043</v>
       </c>
     </row>
     <row r="614">
@@ -7758,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.340808344686275</v>
+        <v>-0.277093496762326</v>
       </c>
     </row>
     <row r="615">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.475836790562825</v>
+        <v>0.531772914176402</v>
       </c>
     </row>
     <row r="617">
@@ -7813,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.0121782122012841</v>
+        <v>0.0520783557934835</v>
       </c>
     </row>
     <row r="620">
@@ -7824,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>0.347009468164937</v>
+        <v>-0.239352368876365</v>
       </c>
     </row>
     <row r="621">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.241658728698487</v>
+        <v>-0.31307908071926</v>
       </c>
     </row>
     <row r="625">
@@ -7945,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.454151858366938</v>
+        <v>-0.310961634672672</v>
       </c>
     </row>
     <row r="632">
@@ -7967,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.181233827740408</v>
+        <v>-0.213668144811886</v>
       </c>
     </row>
     <row r="634">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.160357968069837</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.237842478771536</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.332517741750837</v>
+        <v>-0.280852299762149</v>
       </c>
     </row>
     <row r="638">
@@ -8022,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.418411637771532</v>
+        <v>-0.00394263177177723</v>
       </c>
     </row>
     <row r="639">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.169013903895844</v>
+        <v>-0.175782091855068</v>
       </c>
     </row>
     <row r="647">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.201715956273375</v>
+        <v>-0.172767392481498</v>
       </c>
     </row>
     <row r="649">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.153499393679856</v>
+        <v>-0.220706234085934</v>
       </c>
     </row>
     <row r="652">
@@ -8209,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.154172888944488</v>
+        <v>-0.162264958957565</v>
       </c>
     </row>
     <row r="656">
@@ -8264,7 +8258,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.0945305010980146</v>
       </c>
     </row>
     <row r="661">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.374346588430755</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="662">
@@ -8297,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.566665019945444</v>
+        <v>-0.990275841817236</v>
       </c>
     </row>
     <row r="664">
@@ -8374,7 +8368,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.179649266685795</v>
+        <v>-0.201326604874866</v>
       </c>
     </row>
     <row r="671">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.45881872893855</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="673">
@@ -8418,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.331979579734352</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="675">
@@ -8440,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>0.125018751735046</v>
+        <v>-0.10227018542713</v>
       </c>
     </row>
     <row r="677">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.224310185301595</v>
+        <v>-0.145172750358788</v>
       </c>
     </row>
     <row r="678">
@@ -8462,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.204016653558269</v>
+        <v>-0.424875362905954</v>
       </c>
     </row>
     <row r="679">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.287410552231949</v>
+        <v>-0.488516451158483</v>
       </c>
     </row>
     <row r="680">
@@ -8484,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.149837876084726</v>
+        <v>-0.123522380462693</v>
       </c>
     </row>
     <row r="681">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.209973115633829</v>
+        <v>-0.186636433871154</v>
       </c>
     </row>
     <row r="682">
@@ -8506,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.144130848351192</v>
+        <v>-0.149008017854222</v>
       </c>
     </row>
     <row r="683">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>0.32495158282214</v>
+        <v>0.323728154996278</v>
       </c>
     </row>
     <row r="685">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.164255517362511</v>
+        <v>-0.151014380982736</v>
       </c>
     </row>
     <row r="689">
@@ -8594,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.99069539444185</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="691">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.151937352471295</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="693">
@@ -8627,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.26789279799696</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="694">
@@ -8649,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149263057278303</v>
       </c>
     </row>
     <row r="696">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.1679284744149</v>
+        <v>-0.180246504933183</v>
       </c>
     </row>
     <row r="697">
@@ -8803,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.391872794640005</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="710">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>0.372646364433618</v>
+        <v>0.373733406192427</v>
       </c>
     </row>
     <row r="711">
@@ -8858,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.170269683596466</v>
+        <v>-0.149839725903108</v>
       </c>
     </row>
     <row r="715">
@@ -8880,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.163248641156036</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="717">
@@ -8924,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.170910203143336</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="721">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>0.187424793094958</v>
+        <v>0.268005784191206</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.191346201818939</v>
+        <v>-0.173737856943369</v>
       </c>
     </row>
     <row r="724">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.296750426077034</v>
+        <v>-0.213819336694318</v>
       </c>
     </row>
     <row r="726">
@@ -9001,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.148307170771124</v>
+        <v>-0.164766199960671</v>
       </c>
     </row>
     <row r="728">
@@ -9012,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.137328581497452</v>
+        <v>-0.152254075633215</v>
       </c>
     </row>
     <row r="729">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.169068459543436</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="730">
@@ -9034,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>0.0921176048240069</v>
+        <v>-0.186677441487316</v>
       </c>
     </row>
     <row r="731">
@@ -9056,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.201559782281917</v>
+        <v>-0.467238484262162</v>
       </c>
     </row>
     <row r="733">
@@ -9067,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.166498302115612</v>
+        <v>-0.206983805248073</v>
       </c>
     </row>
     <row r="734">
@@ -9122,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.681509794256285</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="739">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.147803912482804</v>
+        <v>-0.146278826765781</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.238918259606338</v>
+        <v>-0.315025301350119</v>
       </c>
     </row>
     <row r="741">
@@ -9155,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.339567369934918</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="742">
@@ -9177,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.177385327456578</v>
       </c>
     </row>
     <row r="744">
@@ -9188,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.319397357167709</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="745">
@@ -9199,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.16023899103671</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="746">
@@ -9254,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>0.02826595069476</v>
+        <v>0.115413102288912</v>
       </c>
     </row>
     <row r="751">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.165403782099008</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="752">
@@ -9276,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.521609892339834</v>
+        <v>-0.316064557110064</v>
       </c>
     </row>
     <row r="753">
@@ -9287,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.579861905593627</v>
+        <v>-0.454081380890266</v>
       </c>
     </row>
     <row r="754">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.178425224385464</v>
+        <v>-0.17420253754116</v>
       </c>
     </row>
     <row r="756">
@@ -9331,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.318534689344131</v>
+        <v>-0.303298005436341</v>
       </c>
     </row>
     <row r="758">
@@ -9342,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.341376473340859</v>
+        <v>-0.170208013365314</v>
       </c>
     </row>
     <row r="759">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.162814525887787</v>
+        <v>-0.229521109266292</v>
       </c>
     </row>
     <row r="760">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.21392431531593</v>
+        <v>-0.157906022086658</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>0.12919502612434</v>
+        <v>-0.258920814214138</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.240250282440427</v>
+        <v>-0.176394324528204</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>0.194550971832448</v>
+        <v>-0.151477324984084</v>
       </c>
     </row>
     <row r="764">
@@ -9452,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.318364006642787</v>
+        <v>-1.23624364840985</v>
       </c>
     </row>
     <row r="769">
@@ -9463,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.223869385169018</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="770">
@@ -9485,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.301108883901888</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="772">
@@ -9496,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.200039591492313</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="773">
@@ -9507,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.6816865731418</v>
       </c>
     </row>
     <row r="774">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.152211988851522</v>
+        <v>-0.145424806594142</v>
       </c>
     </row>
     <row r="777">
@@ -9562,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.172299332916055</v>
+        <v>-0.168203036468361</v>
       </c>
     </row>
     <row r="779">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.478639335100533</v>
+        <v>-0.301352357852131</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.392921137147021</v>
+        <v>-0.479232309284055</v>
       </c>
     </row>
     <row r="782">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>0.162774238684139</v>
+        <v>-0.15273968742349</v>
       </c>
     </row>
     <row r="785">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.180643801108383</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="787">
@@ -9683,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.223847806480477</v>
+        <v>-0.208798675217583</v>
       </c>
     </row>
     <row r="790">
@@ -9694,7 +9688,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.338930223141602</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="791">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.152276328740501</v>
+        <v>-0.222725505290039</v>
       </c>
     </row>
     <row r="793">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.274440025300382</v>
+        <v>-0.357499955139085</v>
       </c>
     </row>
     <row r="794">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.157564881701373</v>
+        <v>-0.207646450720572</v>
       </c>
     </row>
     <row r="796">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.122101972055747</v>
+        <v>-0.230452299469968</v>
       </c>
     </row>
     <row r="798">
@@ -9837,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.169456275076884</v>
+        <v>-0.185012687135883</v>
       </c>
     </row>
     <row r="804">
@@ -9859,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.53249172274276</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="806">
@@ -9881,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.318132712072802</v>
+        <v>-0.343565093550044</v>
       </c>
     </row>
     <row r="808">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.28732080648199</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.248961168620673</v>
+        <v>-0.232714593071718</v>
       </c>
     </row>
     <row r="810">
@@ -9914,7 +9908,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.19249822767958</v>
+        <v>-0.16764925948285</v>
       </c>
     </row>
     <row r="811">
@@ -9925,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.462239407996057</v>
+        <v>-0.267530815784939</v>
       </c>
     </row>
     <row r="812">
@@ -9947,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.206802977392963</v>
+        <v>-0.188754274860286</v>
       </c>
     </row>
     <row r="814">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.477070666870779</v>
+        <v>-0.462970151264739</v>
       </c>
     </row>
     <row r="815">
@@ -9969,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.325479709762595</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="816">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>0.177394632605015</v>
+        <v>-0.27767333623324</v>
       </c>
     </row>
     <row r="817">
@@ -10013,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.469047909955924</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="820">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.213243659224456</v>
+        <v>-0.160976897291147</v>
       </c>
     </row>
     <row r="821">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.233233192623295</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="822">
@@ -10068,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.190351572233567</v>
+        <v>-0.145767525560349</v>
       </c>
     </row>
     <row r="825">
@@ -10079,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.196554169652857</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="826">
@@ -10101,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.183735141861976</v>
+        <v>-0.210154322799788</v>
       </c>
     </row>
     <row r="828">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.153842133705659</v>
+        <v>-0.151779040196034</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.140453095120767</v>
+        <v>-0.15090378491622</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.19109654810047</v>
       </c>
     </row>
     <row r="831">
@@ -10145,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.165716492223612</v>
+        <v>-0.110439761505277</v>
       </c>
     </row>
     <row r="832">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.326108783120379</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="834">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.189788208606466</v>
+        <v>-0.301922354266699</v>
       </c>
     </row>
     <row r="836">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.1503546408106</v>
+        <v>-0.18893999390279</v>
       </c>
     </row>
     <row r="837">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.163761077742909</v>
+        <v>-0.210391247498507</v>
       </c>
     </row>
     <row r="838">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.182045020329651</v>
+        <v>-0.216978822904251</v>
       </c>
     </row>
     <row r="840">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.322275424142056</v>
+        <v>-0.179473913725124</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.157279591098399</v>
+        <v>-0.155924653744794</v>
       </c>
     </row>
     <row r="845">
@@ -10343,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.20028702323644</v>
+        <v>-0.14896393409095</v>
       </c>
     </row>
     <row r="850">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.287161217545562</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152088957621714</v>
       </c>
     </row>
     <row r="853">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.245595182809297</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="855">
@@ -10409,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.757201817553455</v>
+        <v>-0.513373198456404</v>
       </c>
     </row>
     <row r="856">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.175348753931436</v>
+        <v>-0.15762706232774</v>
       </c>
     </row>
     <row r="857">
@@ -10442,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.289736763621147</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="859">
@@ -10453,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.792060132092442</v>
+        <v>-0.630206981421909</v>
       </c>
     </row>
     <row r="860">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.157274521387003</v>
+        <v>-0.151713570372764</v>
       </c>
     </row>
     <row r="861">
@@ -10508,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.27750246530061</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="865">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.256574896525302</v>
       </c>
     </row>
     <row r="870">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.321726277780133</v>
+        <v>-0.269346324924706</v>
       </c>
     </row>
     <row r="872">
@@ -10596,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.194954943939533</v>
       </c>
     </row>
     <row r="873">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.197152822969635</v>
+        <v>-0.0367352669092247</v>
       </c>
     </row>
     <row r="876">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.0731995055062058</v>
+        <v>0.186445073844425</v>
       </c>
     </row>
     <row r="877">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.177741204171773</v>
+        <v>-0.185474920791035</v>
       </c>
     </row>
     <row r="881">
@@ -10717,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.391378885326265</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="884">
@@ -10728,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.259689531236223</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="885">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.104231276958935</v>
+        <v>-0.119701427424604</v>
       </c>
     </row>
     <row r="886">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.109723274270844</v>
+        <v>0.194424782403186</v>
       </c>
     </row>
     <row r="892">
@@ -10816,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.166827812222741</v>
+        <v>-0.188447101063256</v>
       </c>
     </row>
     <row r="893">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.159159101601936</v>
+        <v>-0.147244949852512</v>
       </c>
     </row>
     <row r="897">
@@ -10882,7 +10876,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.220003839097431</v>
       </c>
     </row>
     <row r="899">
@@ -10893,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.204623096637992</v>
+        <v>-0.252496864395036</v>
       </c>
     </row>
     <row r="900">
@@ -10904,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.309837369258478</v>
+        <v>-0.234244162951843</v>
       </c>
     </row>
     <row r="901">
@@ -10915,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.152605206442113</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="902">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152127142799088</v>
       </c>
     </row>
     <row r="903">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.404895057314297</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="905">
@@ -10970,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.485481940817467</v>
+        <v>-0.203546375120163</v>
       </c>
     </row>
     <row r="907">
@@ -10992,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.169501727837489</v>
+        <v>-0.20957974350444</v>
       </c>
     </row>
     <row r="909">
@@ -11003,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.425867993788831</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="910">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.34579163933266</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="912">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.428249084720992</v>
+        <v>-0.179837216904271</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.193245739500809</v>
       </c>
     </row>
     <row r="918">
@@ -11124,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.772228962798391</v>
+        <v>-0.831550413110561</v>
       </c>
     </row>
     <row r="921">
@@ -11157,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.29548048284278</v>
       </c>
     </row>
     <row r="924">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.349819383533278</v>
+        <v>-0.267813118595358</v>
       </c>
     </row>
     <row r="927">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.167159523768831</v>
+        <v>-0.154440227568863</v>
       </c>
     </row>
     <row r="928">
@@ -11212,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.353737629026483</v>
+        <v>-0.152086295732159</v>
       </c>
     </row>
     <row r="929">
@@ -11223,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.214631742027485</v>
       </c>
     </row>
     <row r="930">
@@ -11256,7 +11250,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.188229006919027</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="933">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.151131054742891</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="934">
@@ -11278,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.200200990414302</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="935">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.191732412812068</v>
+        <v>-0.174634882067134</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.126601569193825</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.763363509783935</v>
+        <v>-0.735264595435667</v>
       </c>
     </row>
     <row r="943">
@@ -11377,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.268368776105365</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>0.0289217437117972</v>
+        <v>0.0519431423168949</v>
       </c>
     </row>
     <row r="946">
@@ -11410,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.26076776290564</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="947">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.151460808445644</v>
+        <v>-0.166520957218208</v>
       </c>
     </row>
     <row r="948">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.179821198067008</v>
       </c>
     </row>
     <row r="949">
@@ -11443,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.224368763370475</v>
+        <v>-0.0705022368719499</v>
       </c>
     </row>
     <row r="950">
@@ -11465,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.227139069960376</v>
+        <v>0.0458855660559869</v>
       </c>
     </row>
     <row r="952">
@@ -11476,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.313888995889075</v>
+        <v>-0.365964841586194</v>
       </c>
     </row>
     <row r="953">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.357135361190021</v>
+        <v>-0.185015882525858</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.173050085546583</v>
+        <v>-0.206191639323687</v>
       </c>
     </row>
     <row r="957">
@@ -11542,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.170033363284454</v>
+        <v>-0.220051312918341</v>
       </c>
     </row>
     <row r="959">
@@ -11586,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.253002042941663</v>
+        <v>-0.173113019402456</v>
       </c>
     </row>
     <row r="963">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.174836985254682</v>
+        <v>-0.171193550982998</v>
       </c>
     </row>
     <row r="964">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.132603576659708</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.170506512426144</v>
+        <v>-0.135268404513408</v>
       </c>
     </row>
     <row r="967">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.149594234964626</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="968">
@@ -11663,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.187905722481795</v>
+        <v>-0.169256928469058</v>
       </c>
     </row>
     <row r="970">
@@ -11674,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.164923450623388</v>
+        <v>-0.164257357962116</v>
       </c>
     </row>
     <row r="971">
@@ -11685,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.422320662232544</v>
+        <v>-0.692746468617542</v>
       </c>
     </row>
     <row r="972">
@@ -11718,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.287385618009017</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="975">
@@ -11729,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.226932719716556</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="976">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.117476212583518</v>
+        <v>-0.120694145471952</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>0.000698971801609161</v>
+        <v>-0.110921540599394</v>
       </c>
     </row>
     <row r="979">
@@ -11784,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.322060037506971</v>
+        <v>-0.249037337912033</v>
       </c>
     </row>
     <row r="981">
@@ -11795,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.102477391168235</v>
+        <v>-0.267140162897852</v>
       </c>
     </row>
     <row r="982">
@@ -11806,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.255384754001195</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="983">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.133220813995854</v>
+        <v>-0.195018642086206</v>
       </c>
     </row>
     <row r="986">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.298857652084446</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="988">
@@ -11872,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.227552266628142</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="989">
@@ -11894,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150019251109056</v>
       </c>
     </row>
     <row r="991">
@@ -11905,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.337799334687828</v>
+        <v>-0.313266334362712</v>
       </c>
     </row>
     <row r="992">
@@ -11916,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.297902693419352</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="993">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.202354387256875</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.34603588533752</v>
+        <v>-0.260575204502648</v>
       </c>
     </row>
     <row r="996">
@@ -11960,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.155333290978103</v>
+        <v>-0.170256600200135</v>
       </c>
     </row>
     <row r="997">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>0.0597848682252484</v>
+        <v>0.0523217844627968</v>
       </c>
     </row>
     <row r="999">
@@ -11993,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.310462335575346</v>
       </c>
     </row>
     <row r="1000">
@@ -12004,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.272190765214059</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="1001">
@@ -12015,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.213254056387755</v>
       </c>
     </row>
     <row r="1002">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.268134435570351</v>
       </c>
     </row>
     <row r="1007">
@@ -12092,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.354877856208593</v>
       </c>
     </row>
     <row r="1009">
@@ -12114,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.333247907334299</v>
       </c>
     </row>
     <row r="1011">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.382295054283249</v>
       </c>
     </row>
     <row r="1014">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.16336754607079</v>
+        <v>-0.257367786269239</v>
       </c>
     </row>
     <row r="1016">
@@ -12213,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.170009656916382</v>
+        <v>-0.336589573146729</v>
       </c>
     </row>
     <row r="1020">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.175812703079052</v>
       </c>
     </row>
     <row r="1024">
@@ -12268,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173472579098201</v>
       </c>
     </row>
     <row r="1025">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16525690458505</v>
       </c>
     </row>
     <row r="1031">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.16430892177393</v>
       </c>
     </row>
     <row r="1034">
@@ -12400,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.192322850045743</v>
       </c>
     </row>
     <row r="1037">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.167214472380342</v>
+        <v>-0.0395718726778016</v>
       </c>
     </row>
     <row r="1038">
@@ -12422,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.184892218723692</v>
       </c>
     </row>
     <row r="1039">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.173844109671102</v>
       </c>
     </row>
     <row r="1042">
@@ -12477,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179757559655824</v>
       </c>
     </row>
     <row r="1044">
@@ -12510,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.169512930736809</v>
+        <v>-0.193522535290991</v>
       </c>
     </row>
     <row r="1047">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0699766426314636</v>
       </c>
     </row>
     <row r="1049">
@@ -12543,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.199556566912432</v>
       </c>
     </row>
     <row r="1050">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.203688717539117</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165415383475766</v>
       </c>
     </row>
     <row r="1052">
@@ -12587,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.398443308329844</v>
       </c>
     </row>
     <row r="1054">
@@ -12598,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181933803806983</v>
       </c>
     </row>
     <row r="1055">
@@ -12609,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.319731477384953</v>
       </c>
     </row>
     <row r="1056">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.223752174502834</v>
       </c>
     </row>
     <row r="1060">
@@ -12664,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174351054095555</v>
       </c>
     </row>
     <row r="1061">
@@ -12675,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.186209293965849</v>
       </c>
     </row>
     <row r="1062">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.680990980405698</v>
       </c>
     </row>
     <row r="1064">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177160819562833</v>
       </c>
     </row>
     <row r="1067">
@@ -12785,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166514813550735</v>
       </c>
     </row>
     <row r="1072">
@@ -12818,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.171778364351963</v>
       </c>
     </row>
     <row r="1075">
@@ -12917,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173933732221071</v>
       </c>
     </row>
     <row r="1084">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.300563578526081</v>
       </c>
     </row>
     <row r="1086">
@@ -12972,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.201200280768672</v>
       </c>
     </row>
     <row r="1089">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.218772144828554</v>
       </c>
     </row>
     <row r="1094">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.134567426828584</v>
       </c>
     </row>
     <row r="1096">
@@ -13082,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.173153711965896</v>
       </c>
     </row>
     <row r="1099">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.13502721941893</v>
       </c>
     </row>
     <row r="1100">
@@ -13104,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.162437952378073</v>
       </c>
     </row>
     <row r="1101">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.16404439018861</v>
+        <v>-0.232939121471281</v>
       </c>
     </row>
     <row r="1104">
@@ -13170,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186538136388836</v>
       </c>
     </row>
     <row r="1107">
@@ -13181,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.233597897491587</v>
       </c>
     </row>
     <row r="1108">
@@ -13203,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165746713795048</v>
       </c>
     </row>
     <row r="1110">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.107925507761625</v>
       </c>
     </row>
     <row r="1116">
@@ -13379,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.124085586190588</v>
+        <v>0.0991277109561753</v>
       </c>
     </row>
     <row r="1126">
@@ -13401,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.357242390314344</v>
       </c>
     </row>
     <row r="1128">
@@ -13412,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.41641632833581</v>
       </c>
     </row>
     <row r="1129">
@@ -13434,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161573428518448</v>
       </c>
     </row>
     <row r="1131">
@@ -13445,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.107646747351933</v>
       </c>
     </row>
     <row r="1132">
@@ -13456,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169022481343117</v>
       </c>
     </row>
     <row r="1133">
@@ -13500,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.168969573872557</v>
       </c>
     </row>
     <row r="1137">
@@ -13533,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.16151972902934</v>
+        <v>-0.156853328262521</v>
       </c>
     </row>
     <row r="1140">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.1599293313245</v>
+        <v>-0.17863601129703</v>
       </c>
     </row>
     <row r="1143">
@@ -13577,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.349520735118952</v>
       </c>
     </row>
     <row r="1144">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.280659336944403</v>
       </c>
     </row>
     <row r="1146">
@@ -13621,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.448070386830456</v>
       </c>
     </row>
     <row r="1148">
@@ -13676,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.49402138435848</v>
       </c>
     </row>
     <row r="1153">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.198626369575906</v>
       </c>
     </row>
     <row r="1157">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.185591082383698</v>
       </c>
     </row>
     <row r="1159">
@@ -13764,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.161699635927184</v>
+        <v>-0.163832882718756</v>
       </c>
     </row>
     <row r="1161">
@@ -13841,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.418125186814661</v>
       </c>
     </row>
     <row r="1168">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.14997493599884</v>
+        <v>0.213426491824817</v>
       </c>
     </row>
     <row r="1171">
@@ -13962,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.168755163883793</v>
       </c>
     </row>
     <row r="1179">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.204865147286286</v>
       </c>
     </row>
     <row r="1181">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0471254232932355</v>
       </c>
     </row>
     <row r="1185">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.840030666389691</v>
       </c>
     </row>
     <row r="1187">
@@ -14061,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227681414256106</v>
       </c>
     </row>
     <row r="1188">
@@ -14072,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227849050377941</v>
       </c>
     </row>
     <row r="1189">
@@ -14105,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170675424318251</v>
       </c>
     </row>
     <row r="1192">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.629561943346402</v>
       </c>
     </row>
     <row r="1195">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0369402092958799</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0419893266973714</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.157447501191734</v>
+        <v>-0.0416449942150721</v>
       </c>
     </row>
     <row r="1199">
@@ -14193,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.170337224465794</v>
+        <v>-0.212054758665769</v>
       </c>
     </row>
     <row r="1200">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.221602901361315</v>
       </c>
     </row>
     <row r="1201">
@@ -14277,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>3.80322468266203</v>
+        <v>3.64442424690355</v>
       </c>
     </row>
     <row r="4">
@@ -15025,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>2.09717531589283</v>
+        <v>1.99364285714286</v>
       </c>
     </row>
     <row r="48">
@@ -15042,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>1.24104151920015</v>
+        <v>1.81421428571429</v>
       </c>
     </row>
     <row r="49">
@@ -15059,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>1.66181024401242</v>
+        <v>2.00278571428571</v>
       </c>
     </row>
     <row r="50">
@@ -15076,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>4.55591011334706</v>
+        <v>1.85242857142857</v>
       </c>
     </row>
     <row r="51">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>5.88522411918137</v>
+        <v>1.90242857142857</v>
       </c>
     </row>
     <row r="52">
@@ -15110,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.47391604178482</v>
+        <v>1.94121428571429</v>
       </c>
     </row>
     <row r="53">
@@ -15127,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>2.05846001909836</v>
+        <v>1.83842857142857</v>
       </c>
     </row>
     <row r="54">
@@ -15144,7 +15138,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E54" t="n">
-        <v>1.65208538211439</v>
+        <v>2.07407142857143</v>
       </c>
     </row>
     <row r="55">
@@ -15178,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>1.87959986688947</v>
+        <v>2.0675</v>
       </c>
     </row>
     <row r="57">
@@ -15195,7 +15189,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E57" t="n">
-        <v>1.01673352831308</v>
+        <v>2.09028571428572</v>
       </c>
     </row>
     <row r="58">
@@ -15212,7 +15206,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>1.70321727017458</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="59">
@@ -15229,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>1.52699609169035</v>
+        <v>2.10257142857143</v>
       </c>
     </row>
     <row r="60">
@@ -15246,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>1.55252689960497</v>
+        <v>2.02185714285714</v>
       </c>
     </row>
     <row r="61">
@@ -15263,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>0.836339413040427</v>
+        <v>1.91107142857143</v>
       </c>
     </row>
     <row r="62">
@@ -15976,13 +15970,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
@@ -15993,13 +15987,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
@@ -16016,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
@@ -16033,7 +16027,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -16050,7 +16044,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>15</v>
@@ -16067,7 +16061,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
@@ -16084,7 +16078,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -16101,7 +16095,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -16118,7 +16112,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
@@ -16135,7 +16129,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
         <v>15</v>
@@ -16152,7 +16146,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
@@ -16163,13 +16157,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
         <v>15</v>
@@ -16180,13 +16174,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
@@ -16197,13 +16191,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -16214,13 +16208,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
@@ -16237,7 +16231,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
@@ -16254,7 +16248,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -16271,7 +16265,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
@@ -16288,7 +16282,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
@@ -16305,7 +16299,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
@@ -16322,7 +16316,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -16339,7 +16333,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
         <v>15</v>
@@ -16350,13 +16344,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D35" t="n">
         <v>15</v>
@@ -16367,13 +16361,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
@@ -16384,13 +16378,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -16401,13 +16395,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -16418,13 +16412,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
@@ -16435,13 +16429,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
         <v>15</v>
@@ -16458,7 +16452,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
         <v>15</v>
@@ -16475,7 +16469,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>15</v>
@@ -16492,7 +16486,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D43" t="n">
         <v>15</v>
@@ -16509,7 +16503,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
         <v>15</v>
@@ -16526,7 +16520,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
         <v>15</v>
@@ -16537,13 +16531,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
         <v>15</v>
@@ -16554,13 +16548,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
@@ -16571,13 +16565,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
@@ -16588,13 +16582,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
@@ -16605,13 +16599,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D50" t="n">
         <v>15</v>
@@ -16622,13 +16616,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D51" t="n">
         <v>15</v>
@@ -16639,13 +16633,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
@@ -16656,13 +16650,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
         <v>15</v>
@@ -16679,7 +16673,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D54" t="n">
         <v>15</v>
@@ -16696,7 +16690,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
         <v>15</v>
@@ -16713,7 +16707,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
         <v>15</v>
@@ -16724,16 +16718,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16741,16 +16735,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16758,16 +16752,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16775,16 +16769,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16792,16 +16786,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16809,16 +16803,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16826,16 +16820,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16843,16 +16837,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16860,16 +16854,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16877,16 +16871,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16900,216 +16894,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" t="n">
-        <v>14</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" t="n">
-        <v>14</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" t="n">
-        <v>14</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" t="n">
-        <v>14</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" t="n">
-        <v>14</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" t="n">
-        <v>14</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
